--- a/data/Data_for_figures_4results/Result2_Indicator_centroids.xlsx
+++ b/data/Data_for_figures_4results/Result2_Indicator_centroids.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\State_SDG\Github\SDG_Interactions-driven-by-Urban_Typologies\data\Data_for_figures_4results\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\City SDG paper\data for governance capacity\WGI_data_072026\1_Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80B68C0A-4416-4182-A7C1-2BC7BA724A9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE7D3EE1-0ECB-41B9-8DE1-6F1D8C8F166C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1152" yWindow="1152" windowWidth="15648" windowHeight="11316" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4704" yWindow="1164" windowWidth="19860" windowHeight="9024" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,165 +25,6 @@
     <t>Cluster</t>
   </si>
   <si>
-    <t>G1.1</t>
-  </si>
-  <si>
-    <t>G1.2</t>
-  </si>
-  <si>
-    <t>G1.3</t>
-  </si>
-  <si>
-    <t>G1.4</t>
-  </si>
-  <si>
-    <t>G1.5</t>
-  </si>
-  <si>
-    <t>G2.1</t>
-  </si>
-  <si>
-    <t>G2.4</t>
-  </si>
-  <si>
-    <t>G3.1</t>
-  </si>
-  <si>
-    <t>G3.2</t>
-  </si>
-  <si>
-    <t>G3.4</t>
-  </si>
-  <si>
-    <t>G3.6</t>
-  </si>
-  <si>
-    <t>G3.7</t>
-  </si>
-  <si>
-    <t>G3.8</t>
-  </si>
-  <si>
-    <t>G3.9</t>
-  </si>
-  <si>
-    <t>G4.2</t>
-  </si>
-  <si>
-    <t>G4.3</t>
-  </si>
-  <si>
-    <t>G4.4</t>
-  </si>
-  <si>
-    <t>G4.5</t>
-  </si>
-  <si>
-    <t>G5.1</t>
-  </si>
-  <si>
-    <t>G5.2</t>
-  </si>
-  <si>
-    <t>G6.1</t>
-  </si>
-  <si>
-    <t>G6.3</t>
-  </si>
-  <si>
-    <t>G6.4</t>
-  </si>
-  <si>
-    <t>G7.1</t>
-  </si>
-  <si>
-    <t>G7.2</t>
-  </si>
-  <si>
-    <t>G7.3</t>
-  </si>
-  <si>
-    <t>G8.1</t>
-  </si>
-  <si>
-    <t>G8.2</t>
-  </si>
-  <si>
-    <t>G8.3</t>
-  </si>
-  <si>
-    <t>G9.1</t>
-  </si>
-  <si>
-    <t>G9.2</t>
-  </si>
-  <si>
-    <t>G9.3</t>
-  </si>
-  <si>
-    <t>G10.2</t>
-  </si>
-  <si>
-    <t>G10.3</t>
-  </si>
-  <si>
-    <t>G10.5</t>
-  </si>
-  <si>
-    <t>G10.7</t>
-  </si>
-  <si>
-    <t>G10.8</t>
-  </si>
-  <si>
-    <t>G11.1</t>
-  </si>
-  <si>
-    <t>G11.2</t>
-  </si>
-  <si>
-    <t>G11.3</t>
-  </si>
-  <si>
-    <t>G11.4</t>
-  </si>
-  <si>
-    <t>G11.5</t>
-  </si>
-  <si>
-    <t>G12.1</t>
-  </si>
-  <si>
-    <t>G12.3</t>
-  </si>
-  <si>
-    <t>G12.4</t>
-  </si>
-  <si>
-    <t>G13.1</t>
-  </si>
-  <si>
-    <t>G13.2</t>
-  </si>
-  <si>
-    <t>G13.3</t>
-  </si>
-  <si>
-    <t>G15.1</t>
-  </si>
-  <si>
-    <t>G15.4</t>
-  </si>
-  <si>
-    <t>G16.1</t>
-  </si>
-  <si>
-    <t>G16.2</t>
-  </si>
-  <si>
-    <t>G16.5</t>
-  </si>
-  <si>
     <t>Cluster1</t>
   </si>
   <si>
@@ -193,10 +34,169 @@
     <t>Cluster3</t>
   </si>
   <si>
-    <t>G2.3</t>
-  </si>
-  <si>
-    <t>G5.4</t>
+    <t>SDG1.1</t>
+  </si>
+  <si>
+    <t>SDG1.2</t>
+  </si>
+  <si>
+    <t>SDG1.3</t>
+  </si>
+  <si>
+    <t>SDG1.4</t>
+  </si>
+  <si>
+    <t>SDG1.5</t>
+  </si>
+  <si>
+    <t>SDG2.1</t>
+  </si>
+  <si>
+    <t>SDG2.3</t>
+  </si>
+  <si>
+    <t>SDG2.4</t>
+  </si>
+  <si>
+    <t>SDG3.1</t>
+  </si>
+  <si>
+    <t>SDG3.2</t>
+  </si>
+  <si>
+    <t>SDG3.4</t>
+  </si>
+  <si>
+    <t>SDG3.6</t>
+  </si>
+  <si>
+    <t>SDG3.7</t>
+  </si>
+  <si>
+    <t>SDG3.8</t>
+  </si>
+  <si>
+    <t>SDG3.9</t>
+  </si>
+  <si>
+    <t>SDG4.2</t>
+  </si>
+  <si>
+    <t>SDG4.3</t>
+  </si>
+  <si>
+    <t>SDG4.4</t>
+  </si>
+  <si>
+    <t>SDG4.5</t>
+  </si>
+  <si>
+    <t>SDG5.1</t>
+  </si>
+  <si>
+    <t>SDG5.2</t>
+  </si>
+  <si>
+    <t>SDG5.4</t>
+  </si>
+  <si>
+    <t>SDG6.1</t>
+  </si>
+  <si>
+    <t>SDG6.3</t>
+  </si>
+  <si>
+    <t>SDG6.4</t>
+  </si>
+  <si>
+    <t>SDG7.1</t>
+  </si>
+  <si>
+    <t>SDG7.2</t>
+  </si>
+  <si>
+    <t>SDG7.3</t>
+  </si>
+  <si>
+    <t>SDG8.1</t>
+  </si>
+  <si>
+    <t>SDG8.2</t>
+  </si>
+  <si>
+    <t>SDG8.3</t>
+  </si>
+  <si>
+    <t>SDG9.1</t>
+  </si>
+  <si>
+    <t>SDG9.2</t>
+  </si>
+  <si>
+    <t>SDG9.3</t>
+  </si>
+  <si>
+    <t>SDG10.2</t>
+  </si>
+  <si>
+    <t>SDG10.3</t>
+  </si>
+  <si>
+    <t>SDG10.5</t>
+  </si>
+  <si>
+    <t>SDG10.7</t>
+  </si>
+  <si>
+    <t>SDG10.8</t>
+  </si>
+  <si>
+    <t>SDG11.1</t>
+  </si>
+  <si>
+    <t>SDG11.2</t>
+  </si>
+  <si>
+    <t>SDG11.3</t>
+  </si>
+  <si>
+    <t>SDG11.4</t>
+  </si>
+  <si>
+    <t>SDG11.5</t>
+  </si>
+  <si>
+    <t>SDG12.1</t>
+  </si>
+  <si>
+    <t>SDG12.3</t>
+  </si>
+  <si>
+    <t>SDG12.4</t>
+  </si>
+  <si>
+    <t>SDG13.1</t>
+  </si>
+  <si>
+    <t>SDG13.2</t>
+  </si>
+  <si>
+    <t>SDG13.3</t>
+  </si>
+  <si>
+    <t>SDG15.1</t>
+  </si>
+  <si>
+    <t>SDG15.4</t>
+  </si>
+  <si>
+    <t>SDG16.1</t>
+  </si>
+  <si>
+    <t>SDG16.2</t>
+  </si>
+  <si>
+    <t>SDG16.5</t>
   </si>
 </sst>
 </file>
@@ -557,174 +557,174 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AN1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AO1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AP1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AQ1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AR1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AS1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AT1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AU1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AV1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AW1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="AX1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="AY1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="AZ1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="BA1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="BB1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="BC1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="W1" s="1" t="s">
+      <c r="BD1" s="1" t="s">
         <v>58</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AE1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="AF1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="AG1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="AH1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="AI1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="AJ1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="AK1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AL1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="AM1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AP1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AQ1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="AR1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="AS1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AT1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="AU1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AV1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="AW1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AX1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AY1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AZ1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="BA1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="BB1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="BC1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="BD1" s="1" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:56" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>54</v>
+        <v>1</v>
       </c>
       <c r="B2">
         <v>-0.18833151596205461</v>
@@ -784,7 +784,7 @@
         <v>-0.13756322285489439</v>
       </c>
       <c r="U2">
-        <v>-0.11099080625811671</v>
+        <v>0.11099080625811671</v>
       </c>
       <c r="V2">
         <v>8.5192813099735781E-2</v>
@@ -835,7 +835,7 @@
         <v>-0.62844067133645476</v>
       </c>
       <c r="AL2">
-        <v>3.7796324849330473E-2</v>
+        <v>-3.7796324849330473E-2</v>
       </c>
       <c r="AM2">
         <v>7.2096980915966558E-2</v>
@@ -894,7 +894,7 @@
     </row>
     <row r="3" spans="1:56" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>55</v>
+        <v>2</v>
       </c>
       <c r="B3">
         <v>-1.108046047886255</v>
@@ -954,7 +954,7 @@
         <v>-0.2149387974417967</v>
       </c>
       <c r="U3">
-        <v>-0.3983688799613454</v>
+        <v>0.3983688799613454</v>
       </c>
       <c r="V3">
         <v>0.82804370298157004</v>
@@ -1005,7 +1005,7 @@
         <v>0.42074667358755452</v>
       </c>
       <c r="AL3">
-        <v>-0.38906513292774031</v>
+        <v>0.38906513292774031</v>
       </c>
       <c r="AM3">
         <v>0.34053376248636102</v>
@@ -1064,7 +1064,7 @@
     </row>
     <row r="4" spans="1:56" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>56</v>
+        <v>3</v>
       </c>
       <c r="B4">
         <v>0.826087357179209</v>
@@ -1124,7 +1124,7 @@
         <v>0.32367641223788052</v>
       </c>
       <c r="U4">
-        <v>0.36701165951700149</v>
+        <v>-0.36701165951700149</v>
       </c>
       <c r="V4">
         <v>-0.52747952847619539</v>
@@ -1175,7 +1175,7 @@
         <v>0.81859676900305989</v>
       </c>
       <c r="AL4">
-        <v>0.12194836059207879</v>
+        <v>-0.12194836059207879</v>
       </c>
       <c r="AM4">
         <v>-0.27687865147529211</v>
